--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260615.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260615.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.78%</t>
+          <t>9.99%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.72%</t>
+          <t>9.94%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.73%</t>
+          <t>8.83%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>8.03%</t>
+          <t>8.07%</t>
         </is>
       </c>
     </row>
@@ -704,46 +704,46 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.35%</t>
+          <t>5.27%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>DUK US</t>
+          <t>BE UN</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>杜克能源公司</t>
+          <t>Bloom Energy Corp</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>116,148</t>
+          <t>54,828</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.14%</t>
+          <t>4.21%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>BE UN</t>
+          <t>DUK US</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Bloom Energy Corp</t>
+          <t>杜克能源公司</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>54,828</t>
+          <t>116,148</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>3.31%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>62,978</t>
+          <t>65,978</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>3.12%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>2.97%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.50%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.20%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.08%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
@@ -968,95 +968,95 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.32%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>PEG US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>大眾服務企業集團公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>41,158</t>
+          <t>55,658</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>PEG US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>大眾服務企業集團公司</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>55,658</t>
+          <t>41,158</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>愛迪生國際</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>57,306</t>
+          <t>36,381</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>愛迪生國際</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>36,381</t>
+          <t>57,306</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
@@ -1100,134 +1100,134 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>34,069</t>
+          <t>24,908</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>ACM UN</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>艾奕康</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>52,626</t>
+          <t>34,069</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>24,908</t>
+          <t>5,507</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>5,507</t>
+          <t>10,076</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>DTE US</t>
+          <t>ACM UN</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>DTE能源</t>
+          <t>艾奕康</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>23,174</t>
+          <t>52,626</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>30,851</t>
+          <t>14,830</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,44 +1239,44 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>DTE US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>DTE能源</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>14,830</t>
+          <t>23,174</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>9,076</t>
+          <t>30,851</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1298,51 +1298,51 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>TTEK UW</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>德照科技公司</t>
+          <t>PPL公司</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>106,381</t>
+          <t>84,012</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>TTEK UW</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>PPL公司</t>
+          <t>德照科技公司</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>84,012</t>
+          <t>106,381</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
@@ -1408,46 +1408,46 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>202606ESM6</t>
+          <t>POWL US</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>小型S＆P 500股價指數</t>
+          <t>Powell工業公司</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7,640</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>0.65%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>POWL US</t>
+          <t>202609ESU6</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Powell工業公司</t>
+          <t>小型S＆P 500股價指數</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>7,640</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,66 +1459,66 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>LNT US</t>
+          <t>VICR US</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>聯合能源公司</t>
+          <t>懷克爾公司</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>28,850</t>
+          <t>6,577</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>LNT US</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>聯合能源公司</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>48,660</t>
+          <t>28,850</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>VICR US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>懷克爾公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>6,577</t>
+          <t>48,660</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
@@ -1562,68 +1562,68 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>AES US</t>
+          <t>MYRG US</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>愛伊斯公司</t>
+          <t>MYR集團公司</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>105,753</t>
+          <t>4,086</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>ENPH US</t>
+          <t>AES US</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Enphase能源公司</t>
+          <t>愛伊斯公司</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>26,319</t>
+          <t>105,753</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>MYRG US</t>
+          <t>ENPH US</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>MYR集團公司</t>
+          <t>Enphase能源公司</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>3,086</t>
+          <t>26,319</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
@@ -1716,119 +1716,23 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>0.02%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>MEI US</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>邁梭電子公司</t>
-        </is>
-      </c>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="D72" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>AMSC US</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>美國超導公司</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>NXT US</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>NEXTracker公司</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>OGE UN</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>OGE Energy Corp</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>SWX US</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>西南天然氣控股公司</t>
-        </is>
-      </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="D76" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+          <t>142,887,553</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
